--- a/crates/pmcp-workbook-compiler/tests/fixtures/tax-calc.xlsx
+++ b/crates/pmcp-workbook-compiler/tests/fixtures/tax-calc.xlsx
@@ -12,6 +12,9 @@
     <sheet name="3_Outputs" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="in_gross_income">'1_Inputs'!$B$2</definedName>
+    <definedName name="in_filing_status">'1_Inputs'!$B$3</definedName>
+    <definedName name="in_deductions">'1_Inputs'!$B$4</definedName>
     <definedName name="out_effective_rate">'3_Outputs'!$B$4</definedName>
     <definedName name="out_marginal_rate">'3_Outputs'!$B$5</definedName>
     <definedName name="out_tax_owed">'3_Outputs'!$B$3</definedName>
